--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nlion\OneDrive\문서\GitHub\Lotto-wizard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BD39459-59B2-419B-892E-C4488AD3AE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411C8362-A63A-4BA4-B87A-BF4AAF28F508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nlion\OneDrive\문서\GitHub\Lotto-wizard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411C8362-A63A-4BA4-B87A-BF4AAF28F508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5C4A15-541B-42E3-94AC-5FAB2AA608FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
